--- a/annotation/excel/zajkeskn_annotation.xlsx
+++ b/annotation/excel/zajkeskn_annotation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nzajkeskovic/Compsci/University/4th/cs4nl3/4nl3-project/annotation/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B1BAF67-C22D-684E-BB7E-0DE5A0800665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E29520-B0D5-F64E-9022-0A6C730B0DB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16060" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="initial" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3180" uniqueCount="1601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3225" uniqueCount="1601">
   <si>
     <t>instance_id</t>
   </si>
@@ -15109,7 +15109,9 @@
       <c r="E2" s="2" t="s">
         <v>1420</v>
       </c>
-      <c r="F2" s="2"/>
+      <c r="F2" s="2" t="s">
+        <v>1596</v>
+      </c>
       <c r="G2" s="2" t="s">
         <v>15</v>
       </c>
@@ -15137,7 +15139,9 @@
       <c r="E3" s="2" t="s">
         <v>1426</v>
       </c>
-      <c r="F3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>1600</v>
+      </c>
       <c r="G3" s="2" t="s">
         <v>15</v>
       </c>
@@ -15165,7 +15169,9 @@
       <c r="E4" s="2" t="s">
         <v>1430</v>
       </c>
-      <c r="F4" s="2"/>
+      <c r="F4" s="2" t="s">
+        <v>1596</v>
+      </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
       </c>
@@ -15193,7 +15199,9 @@
       <c r="E5" s="2" t="s">
         <v>1434</v>
       </c>
-      <c r="F5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>1597</v>
+      </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
       </c>
@@ -15221,7 +15229,9 @@
       <c r="E6" s="2" t="s">
         <v>1438</v>
       </c>
-      <c r="F6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>1600</v>
+      </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
       </c>
@@ -15249,7 +15259,9 @@
       <c r="E7" s="2" t="s">
         <v>1442</v>
       </c>
-      <c r="F7" s="2"/>
+      <c r="F7" s="2" t="s">
+        <v>1599</v>
+      </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
       </c>
@@ -15277,7 +15289,9 @@
       <c r="E8" s="2" t="s">
         <v>1446</v>
       </c>
-      <c r="F8" s="2"/>
+      <c r="F8" s="2" t="s">
+        <v>1596</v>
+      </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
       </c>
@@ -15305,7 +15319,9 @@
       <c r="E9" s="2" t="s">
         <v>1450</v>
       </c>
-      <c r="F9" s="2"/>
+      <c r="F9" s="2" t="s">
+        <v>1599</v>
+      </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
       </c>
@@ -15333,7 +15349,9 @@
       <c r="E10" s="2" t="s">
         <v>1454</v>
       </c>
-      <c r="F10" s="2"/>
+      <c r="F10" s="2" t="s">
+        <v>1600</v>
+      </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
       </c>
@@ -15361,7 +15379,9 @@
       <c r="E11" s="2" t="s">
         <v>1458</v>
       </c>
-      <c r="F11" s="2"/>
+      <c r="F11" s="2" t="s">
+        <v>1600</v>
+      </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
       </c>
@@ -15389,7 +15409,9 @@
       <c r="E12" s="2" t="s">
         <v>1461</v>
       </c>
-      <c r="F12" s="2"/>
+      <c r="F12" s="2" t="s">
+        <v>1598</v>
+      </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
       </c>
@@ -15417,7 +15439,9 @@
       <c r="E13" s="2" t="s">
         <v>1465</v>
       </c>
-      <c r="F13" s="2"/>
+      <c r="F13" s="2" t="s">
+        <v>1598</v>
+      </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
       </c>
@@ -15445,7 +15469,9 @@
       <c r="E14" s="2" t="s">
         <v>1469</v>
       </c>
-      <c r="F14" s="2"/>
+      <c r="F14" s="2" t="s">
+        <v>1599</v>
+      </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
       </c>
@@ -15473,7 +15499,9 @@
       <c r="E15" s="2" t="s">
         <v>1473</v>
       </c>
-      <c r="F15" s="2"/>
+      <c r="F15" s="2" t="s">
+        <v>1600</v>
+      </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
       </c>
@@ -15501,7 +15529,9 @@
       <c r="E16" s="2" t="s">
         <v>1477</v>
       </c>
-      <c r="F16" s="2"/>
+      <c r="F16" s="2" t="s">
+        <v>1600</v>
+      </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
       </c>
@@ -15529,7 +15559,9 @@
       <c r="E17" s="2" t="s">
         <v>1481</v>
       </c>
-      <c r="F17" s="2"/>
+      <c r="F17" s="2" t="s">
+        <v>1598</v>
+      </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
       </c>
@@ -15557,7 +15589,9 @@
       <c r="E18" s="2" t="s">
         <v>1485</v>
       </c>
-      <c r="F18" s="2"/>
+      <c r="F18" s="2" t="s">
+        <v>1600</v>
+      </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
       </c>
@@ -15585,7 +15619,9 @@
       <c r="E19" s="2" t="s">
         <v>1489</v>
       </c>
-      <c r="F19" s="2"/>
+      <c r="F19" s="2" t="s">
+        <v>1599</v>
+      </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
       </c>
@@ -15613,7 +15649,9 @@
       <c r="E20" s="2" t="s">
         <v>1493</v>
       </c>
-      <c r="F20" s="2"/>
+      <c r="F20" s="2" t="s">
+        <v>1599</v>
+      </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
       </c>
@@ -15641,7 +15679,9 @@
       <c r="E21" s="2" t="s">
         <v>1497</v>
       </c>
-      <c r="F21" s="2"/>
+      <c r="F21" s="2" t="s">
+        <v>1598</v>
+      </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
       </c>
@@ -15669,7 +15709,9 @@
       <c r="E22" s="2" t="s">
         <v>1501</v>
       </c>
-      <c r="F22" s="2"/>
+      <c r="F22" s="2" t="s">
+        <v>1598</v>
+      </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
       </c>
@@ -15697,7 +15739,9 @@
       <c r="E23" s="2" t="s">
         <v>1505</v>
       </c>
-      <c r="F23" s="2"/>
+      <c r="F23" s="2" t="s">
+        <v>1599</v>
+      </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
       </c>
@@ -15725,7 +15769,9 @@
       <c r="E24" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="F24" s="2"/>
+      <c r="F24" s="2" t="s">
+        <v>1598</v>
+      </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
       </c>
@@ -15753,7 +15799,9 @@
       <c r="E25" s="2" t="s">
         <v>1513</v>
       </c>
-      <c r="F25" s="2"/>
+      <c r="F25" s="2" t="s">
+        <v>1600</v>
+      </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
       </c>
@@ -15781,7 +15829,9 @@
       <c r="E26" s="2" t="s">
         <v>1516</v>
       </c>
-      <c r="F26" s="2"/>
+      <c r="F26" s="2" t="s">
+        <v>1599</v>
+      </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
       </c>
@@ -15809,7 +15859,9 @@
       <c r="E27" s="2" t="s">
         <v>1520</v>
       </c>
-      <c r="F27" s="2"/>
+      <c r="F27" s="2" t="s">
+        <v>1597</v>
+      </c>
       <c r="G27" s="2" t="s">
         <v>15</v>
       </c>
@@ -15837,7 +15889,9 @@
       <c r="E28" s="2" t="s">
         <v>1524</v>
       </c>
-      <c r="F28" s="2"/>
+      <c r="F28" s="2" t="s">
+        <v>1599</v>
+      </c>
       <c r="G28" s="2" t="s">
         <v>15</v>
       </c>
@@ -15865,7 +15919,9 @@
       <c r="E29" s="2" t="s">
         <v>1528</v>
       </c>
-      <c r="F29" s="2"/>
+      <c r="F29" s="2" t="s">
+        <v>1600</v>
+      </c>
       <c r="G29" s="2" t="s">
         <v>15</v>
       </c>
@@ -15893,7 +15949,9 @@
       <c r="E30" s="2" t="s">
         <v>1532</v>
       </c>
-      <c r="F30" s="2"/>
+      <c r="F30" s="2" t="s">
+        <v>1599</v>
+      </c>
       <c r="G30" s="2" t="s">
         <v>15</v>
       </c>
@@ -15921,7 +15979,9 @@
       <c r="E31" s="2" t="s">
         <v>1536</v>
       </c>
-      <c r="F31" s="2"/>
+      <c r="F31" s="2" t="s">
+        <v>1599</v>
+      </c>
       <c r="G31" s="2" t="s">
         <v>15</v>
       </c>
@@ -15949,7 +16009,9 @@
       <c r="E32" s="2" t="s">
         <v>1540</v>
       </c>
-      <c r="F32" s="2"/>
+      <c r="F32" s="2" t="s">
+        <v>1600</v>
+      </c>
       <c r="G32" s="2" t="s">
         <v>15</v>
       </c>
@@ -15977,7 +16039,9 @@
       <c r="E33" s="2" t="s">
         <v>1544</v>
       </c>
-      <c r="F33" s="2"/>
+      <c r="F33" s="2" t="s">
+        <v>1597</v>
+      </c>
       <c r="G33" s="2" t="s">
         <v>15</v>
       </c>
@@ -16005,7 +16069,9 @@
       <c r="E34" s="2" t="s">
         <v>1548</v>
       </c>
-      <c r="F34" s="2"/>
+      <c r="F34" s="2" t="s">
+        <v>1599</v>
+      </c>
       <c r="G34" s="2" t="s">
         <v>15</v>
       </c>
@@ -16033,7 +16099,9 @@
       <c r="E35" s="2" t="s">
         <v>1552</v>
       </c>
-      <c r="F35" s="2"/>
+      <c r="F35" s="2" t="s">
+        <v>1596</v>
+      </c>
       <c r="G35" s="2" t="s">
         <v>15</v>
       </c>
@@ -16061,7 +16129,9 @@
       <c r="E36" s="2" t="s">
         <v>1556</v>
       </c>
-      <c r="F36" s="2"/>
+      <c r="F36" s="2" t="s">
+        <v>1596</v>
+      </c>
       <c r="G36" s="2" t="s">
         <v>15</v>
       </c>
@@ -16089,7 +16159,9 @@
       <c r="E37" s="2" t="s">
         <v>1559</v>
       </c>
-      <c r="F37" s="2"/>
+      <c r="F37" s="2" t="s">
+        <v>1599</v>
+      </c>
       <c r="G37" s="2" t="s">
         <v>15</v>
       </c>
@@ -16117,7 +16189,9 @@
       <c r="E38" s="2" t="s">
         <v>1563</v>
       </c>
-      <c r="F38" s="2"/>
+      <c r="F38" s="2" t="s">
+        <v>1598</v>
+      </c>
       <c r="G38" s="2" t="s">
         <v>15</v>
       </c>
@@ -16145,7 +16219,9 @@
       <c r="E39" s="2" t="s">
         <v>1567</v>
       </c>
-      <c r="F39" s="2"/>
+      <c r="F39" s="2" t="s">
+        <v>1598</v>
+      </c>
       <c r="G39" s="2" t="s">
         <v>15</v>
       </c>
@@ -16173,7 +16249,9 @@
       <c r="E40" s="2" t="s">
         <v>1571</v>
       </c>
-      <c r="F40" s="2"/>
+      <c r="F40" s="2" t="s">
+        <v>1599</v>
+      </c>
       <c r="G40" s="2" t="s">
         <v>15</v>
       </c>
@@ -16201,7 +16279,9 @@
       <c r="E41" s="2" t="s">
         <v>1575</v>
       </c>
-      <c r="F41" s="2"/>
+      <c r="F41" s="2" t="s">
+        <v>1598</v>
+      </c>
       <c r="G41" s="2" t="s">
         <v>15</v>
       </c>
@@ -16229,7 +16309,9 @@
       <c r="E42" s="2" t="s">
         <v>1579</v>
       </c>
-      <c r="F42" s="2"/>
+      <c r="F42" s="2" t="s">
+        <v>1600</v>
+      </c>
       <c r="G42" s="2" t="s">
         <v>15</v>
       </c>
@@ -16257,7 +16339,9 @@
       <c r="E43" s="2" t="s">
         <v>1583</v>
       </c>
-      <c r="F43" s="2"/>
+      <c r="F43" s="2" t="s">
+        <v>1596</v>
+      </c>
       <c r="G43" s="2" t="s">
         <v>15</v>
       </c>
@@ -16285,7 +16369,9 @@
       <c r="E44" s="2" t="s">
         <v>1587</v>
       </c>
-      <c r="F44" s="2"/>
+      <c r="F44" s="2" t="s">
+        <v>1599</v>
+      </c>
       <c r="G44" s="2" t="s">
         <v>15</v>
       </c>
@@ -16313,7 +16399,9 @@
       <c r="E45" s="2" t="s">
         <v>1591</v>
       </c>
-      <c r="F45" s="2"/>
+      <c r="F45" s="2" t="s">
+        <v>1598</v>
+      </c>
       <c r="G45" s="2" t="s">
         <v>15</v>
       </c>
@@ -16341,7 +16429,9 @@
       <c r="E46" s="2" t="s">
         <v>1595</v>
       </c>
-      <c r="F46" s="2"/>
+      <c r="F46" s="2" t="s">
+        <v>1600</v>
+      </c>
       <c r="G46" s="2" t="s">
         <v>15</v>
       </c>
